--- a/Result_optimized_bank.xlsx
+++ b/Result_optimized_bank.xlsx
@@ -14,25 +14,65 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>H &amp; M Hennes &amp; Mauritz AB (XSTO:HM B)</t>
+  </si>
+  <si>
+    <t>ASTRAZENECA PLC (XSTO:AZN)</t>
+  </si>
+  <si>
+    <t>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</t>
+  </si>
+  <si>
+    <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
+  </si>
+  <si>
+    <t>Ratos AB (XSTO:RATO B)</t>
+  </si>
+  <si>
+    <t>Investment AB Latour (XSTO:LATO B)</t>
+  </si>
+  <si>
+    <t>AT&amp;T INC. (XNYS:T)</t>
+  </si>
+  <si>
+    <t>Investor AB (XSTO:INVE B)</t>
+  </si>
+  <si>
+    <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
+  </si>
+  <si>
+    <t>Kinnevik AB (XSTO:KINV B)</t>
+  </si>
+  <si>
+    <t>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</t>
+  </si>
+  <si>
+    <t>NCC AB (XSTO:NCC B)</t>
+  </si>
+  <si>
+    <t>EQT AB (XSTO:EQT)</t>
+  </si>
+  <si>
+    <t>Atlas Copco AB (XSTO:ATCO B)</t>
+  </si>
+  <si>
+    <t>Castellum AB (XSTO:CAST)</t>
+  </si>
+  <si>
+    <t>Axfood AB (XSTO:AXFO)</t>
+  </si>
+  <si>
+    <t>Swedbank AB (XSTO:SWED A)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -48,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,30 +96,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -374,17 +396,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2">
-        <v>0</v>
+      <c r="B1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Result_optimized_bank.xlsx
+++ b/Result_optimized_bank.xlsx
@@ -16,6 +16,39 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
+    <t>Ratos AB (XSTO:RATO B)</t>
+  </si>
+  <si>
+    <t>Investment AB Latour (XSTO:LATO B)</t>
+  </si>
+  <si>
+    <t>AT&amp;T INC. (XNYS:T)</t>
+  </si>
+  <si>
+    <t>Investor AB (XSTO:INVE B)</t>
+  </si>
+  <si>
+    <t>EQT AB (XSTO:EQT)</t>
+  </si>
+  <si>
+    <t>Castellum AB (XSTO:CAST)</t>
+  </si>
+  <si>
+    <t>Axfood AB (XSTO:AXFO)</t>
+  </si>
+  <si>
+    <t>Kinnevik AB (XSTO:KINV B)</t>
+  </si>
+  <si>
+    <t>Atlas Copco AB (XSTO:ATCO B)</t>
+  </si>
+  <si>
+    <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
+  </si>
+  <si>
+    <t>Swedbank AB (XSTO:SWED A)</t>
+  </si>
+  <si>
     <t>H &amp; M Hennes &amp; Mauritz AB (XSTO:HM B)</t>
   </si>
   <si>
@@ -25,46 +58,13 @@
     <t>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</t>
   </si>
   <si>
+    <t>NCC AB (XSTO:NCC B)</t>
+  </si>
+  <si>
     <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
   </si>
   <si>
-    <t>Ratos AB (XSTO:RATO B)</t>
-  </si>
-  <si>
-    <t>Investment AB Latour (XSTO:LATO B)</t>
-  </si>
-  <si>
-    <t>AT&amp;T INC. (XNYS:T)</t>
-  </si>
-  <si>
-    <t>Investor AB (XSTO:INVE B)</t>
-  </si>
-  <si>
-    <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
-  </si>
-  <si>
-    <t>Kinnevik AB (XSTO:KINV B)</t>
-  </si>
-  <si>
     <t>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</t>
-  </si>
-  <si>
-    <t>NCC AB (XSTO:NCC B)</t>
-  </si>
-  <si>
-    <t>EQT AB (XSTO:EQT)</t>
-  </si>
-  <si>
-    <t>Atlas Copco AB (XSTO:ATCO B)</t>
-  </si>
-  <si>
-    <t>Castellum AB (XSTO:CAST)</t>
-  </si>
-  <si>
-    <t>Axfood AB (XSTO:AXFO)</t>
-  </si>
-  <si>
-    <t>Swedbank AB (XSTO:SWED A)</t>
   </si>
 </sst>
 </file>
@@ -404,7 +404,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -412,7 +412,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -420,7 +420,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -428,7 +428,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -436,7 +436,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -444,7 +444,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -452,7 +452,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -468,7 +468,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -476,7 +476,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -484,7 +484,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -492,7 +492,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -500,7 +500,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -508,7 +508,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -516,7 +516,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -524,7 +524,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -532,7 +532,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Result_optimized_bank.xlsx
+++ b/Result_optimized_bank.xlsx
@@ -16,6 +16,27 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
+    <t>Swedbank AB (XSTO:SWED A)</t>
+  </si>
+  <si>
+    <t>H &amp; M Hennes &amp; Mauritz AB (XSTO:HM B)</t>
+  </si>
+  <si>
+    <t>ASTRAZENECA PLC (XSTO:AZN)</t>
+  </si>
+  <si>
+    <t>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</t>
+  </si>
+  <si>
+    <t>NCC AB (XSTO:NCC B)</t>
+  </si>
+  <si>
+    <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
+  </si>
+  <si>
+    <t>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</t>
+  </si>
+  <si>
     <t>Ratos AB (XSTO:RATO B)</t>
   </si>
   <si>
@@ -44,27 +65,6 @@
   </si>
   <si>
     <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
-  </si>
-  <si>
-    <t>Swedbank AB (XSTO:SWED A)</t>
-  </si>
-  <si>
-    <t>H &amp; M Hennes &amp; Mauritz AB (XSTO:HM B)</t>
-  </si>
-  <si>
-    <t>ASTRAZENECA PLC (XSTO:AZN)</t>
-  </si>
-  <si>
-    <t>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</t>
-  </si>
-  <si>
-    <t>NCC AB (XSTO:NCC B)</t>
-  </si>
-  <si>
-    <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
-  </si>
-  <si>
-    <t>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</t>
   </si>
 </sst>
 </file>
@@ -420,7 +420,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -444,7 +444,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -452,7 +452,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -476,7 +476,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -484,7 +484,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -492,7 +492,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -500,7 +500,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -508,7 +508,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -516,7 +516,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -524,7 +524,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -532,7 +532,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Result_optimized_bank.xlsx
+++ b/Result_optimized_bank.xlsx
@@ -14,65 +14,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Swedbank AB (XSTO:SWED A)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
   </si>
   <si>
     <t>H &amp; M Hennes &amp; Mauritz AB (XSTO:HM B)</t>
   </si>
   <si>
-    <t>ASTRAZENECA PLC (XSTO:AZN)</t>
+    <t>Investor AB (XSTO:INVE B)</t>
+  </si>
+  <si>
+    <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
+  </si>
+  <si>
+    <t>Kinnevik AB (XSTO:KINV B)</t>
+  </si>
+  <si>
+    <t>Atlas Copco AB (XSTO:ATCO B)</t>
   </si>
   <si>
     <t>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</t>
   </si>
   <si>
-    <t>NCC AB (XSTO:NCC B)</t>
-  </si>
-  <si>
-    <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
-  </si>
-  <si>
-    <t>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</t>
-  </si>
-  <si>
-    <t>Ratos AB (XSTO:RATO B)</t>
-  </si>
-  <si>
-    <t>Investment AB Latour (XSTO:LATO B)</t>
-  </si>
-  <si>
     <t>AT&amp;T INC. (XNYS:T)</t>
   </si>
   <si>
-    <t>Investor AB (XSTO:INVE B)</t>
-  </si>
-  <si>
     <t>EQT AB (XSTO:EQT)</t>
   </si>
   <si>
-    <t>Castellum AB (XSTO:CAST)</t>
-  </si>
-  <si>
-    <t>Axfood AB (XSTO:AXFO)</t>
-  </si>
-  <si>
-    <t>Kinnevik AB (XSTO:KINV B)</t>
-  </si>
-  <si>
-    <t>Atlas Copco AB (XSTO:ATCO B)</t>
-  </si>
-  <si>
-    <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
+    <t>Yearly devidend</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -88,7 +75,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,12 +83,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,26 +401,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -423,23 +428,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -447,23 +452,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -471,68 +476,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:5">
+      <c r="E10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="E11">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Result_optimized_bank.xlsx
+++ b/Result_optimized_bank.xlsx
@@ -409,7 +409,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -417,7 +417,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -441,7 +441,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -457,7 +457,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -465,7 +465,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -483,7 +483,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="E11">
-        <v>120</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Result_optimized_bank.xlsx
+++ b/Result_optimized_bank.xlsx
@@ -16,31 +16,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
-  </si>
-  <si>
-    <t>H &amp; M Hennes &amp; Mauritz AB (XSTO:HM B)</t>
-  </si>
-  <si>
-    <t>Investor AB (XSTO:INVE B)</t>
-  </si>
-  <si>
-    <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
-  </si>
-  <si>
-    <t>Kinnevik AB (XSTO:KINV B)</t>
-  </si>
-  <si>
-    <t>Atlas Copco AB (XSTO:ATCO B)</t>
-  </si>
-  <si>
-    <t>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</t>
-  </si>
-  <si>
-    <t>AT&amp;T INC. (XNYS:T)</t>
-  </si>
-  <si>
-    <t>EQT AB (XSTO:EQT)</t>
+    <t>NCC AB (XSTO:NCC B)</t>
+  </si>
+  <si>
+    <t>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</t>
+  </si>
+  <si>
+    <t>Castellum AB (XSTO:CAST)</t>
+  </si>
+  <si>
+    <t>Axfood AB (XSTO:AXFO)</t>
+  </si>
+  <si>
+    <t>Swedbank AB (XSTO:SWED A)</t>
+  </si>
+  <si>
+    <t>Investment AB Latour (XSTO:LATO B)</t>
+  </si>
+  <si>
+    <t>Ratos AB (XSTO:RATO B)</t>
+  </si>
+  <si>
+    <t>ASTRAZENECA PLC (XSTO:AZN)</t>
+  </si>
+  <si>
+    <t>Klovern AB (XSTO:KLOV B)</t>
   </si>
   <si>
     <t>Yearly devidend</t>
@@ -409,7 +409,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -417,7 +417,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -433,7 +433,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -441,7 +441,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -465,7 +465,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -473,7 +473,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -483,7 +483,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="E11">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Result_optimized_bank.xlsx
+++ b/Result_optimized_bank.xlsx
@@ -16,31 +16,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>NCC AB (XSTO:NCC B)</t>
-  </si>
-  <si>
-    <t>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</t>
-  </si>
-  <si>
-    <t>Castellum AB (XSTO:CAST)</t>
-  </si>
-  <si>
-    <t>Axfood AB (XSTO:AXFO)</t>
-  </si>
-  <si>
-    <t>Swedbank AB (XSTO:SWED A)</t>
-  </si>
-  <si>
-    <t>Investment AB Latour (XSTO:LATO B)</t>
-  </si>
-  <si>
-    <t>Ratos AB (XSTO:RATO B)</t>
-  </si>
-  <si>
-    <t>ASTRAZENECA PLC (XSTO:AZN)</t>
-  </si>
-  <si>
-    <t>Klovern AB (XSTO:KLOV B)</t>
+    <t>Telefonaktiebolaget LM Ericsson (XSTO:ERIC B)</t>
+  </si>
+  <si>
+    <t>H &amp; M Hennes &amp; Mauritz AB (XSTO:HM B)</t>
+  </si>
+  <si>
+    <t>Investor AB (XSTO:INVE B)</t>
+  </si>
+  <si>
+    <t>AUTOLIV, INC. (XSTO:ALIV SDB)</t>
+  </si>
+  <si>
+    <t>Kinnevik AB (XSTO:KINV B)</t>
+  </si>
+  <si>
+    <t>Atlas Copco AB (XSTO:ATCO B)</t>
+  </si>
+  <si>
+    <t>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</t>
+  </si>
+  <si>
+    <t>AT&amp;T INC. (XNYS:T)</t>
+  </si>
+  <si>
+    <t>EQT AB (XSTO:EQT)</t>
   </si>
   <si>
     <t>Yearly devidend</t>
@@ -409,7 +409,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -417,7 +417,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -433,7 +433,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -441,7 +441,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -473,7 +473,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -483,7 +483,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="E11">
-        <v>98</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
